--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E904"/>
+  <dimension ref="A1:E905"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15761,6 +15761,23 @@
         <v>4009.94</v>
       </c>
     </row>
+    <row r="905" spans="1:5">
+      <c r="A905" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B905">
+        <v>12726.29</v>
+      </c>
+      <c r="C905">
+        <v>195.97</v>
+      </c>
+      <c r="D905">
+        <v>5254.66</v>
+      </c>
+      <c r="E905">
+        <v>4027.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E905"/>
+  <dimension ref="A1:E906"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15778,6 +15778,23 @@
         <v>4027.28</v>
       </c>
     </row>
+    <row r="906" spans="1:5">
+      <c r="A906" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B906">
+        <v>12175.73</v>
+      </c>
+      <c r="C906">
+        <v>181.15</v>
+      </c>
+      <c r="D906">
+        <v>4944.53</v>
+      </c>
+      <c r="E906">
+        <v>3716.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E906"/>
+  <dimension ref="A1:E907"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15795,6 +15795,23 @@
         <v>3716.93</v>
       </c>
     </row>
+    <row r="907" spans="1:5">
+      <c r="A907" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B907">
+        <v>12241.76</v>
+      </c>
+      <c r="C907">
+        <v>177.93</v>
+      </c>
+      <c r="D907">
+        <v>4884.27</v>
+      </c>
+      <c r="E907">
+        <v>3701.79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E907"/>
+  <dimension ref="A1:E908"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15812,6 +15812,23 @@
         <v>3701.79</v>
       </c>
     </row>
+    <row r="908" spans="1:5">
+      <c r="A908" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B908">
+        <v>12435.62</v>
+      </c>
+      <c r="C908">
+        <v>182.74</v>
+      </c>
+      <c r="D908">
+        <v>5028.64</v>
+      </c>
+      <c r="E908">
+        <v>3827.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E908"/>
+  <dimension ref="A1:E909"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15829,6 +15829,23 @@
         <v>3827.99</v>
       </c>
     </row>
+    <row r="909" spans="1:5">
+      <c r="A909" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B909">
+        <v>12235.51</v>
+      </c>
+      <c r="C909">
+        <v>185.21</v>
+      </c>
+      <c r="D909">
+        <v>4977.59</v>
+      </c>
+      <c r="E909">
+        <v>3882.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E909"/>
+  <dimension ref="A1:E910"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15846,6 +15846,23 @@
         <v>3882.59</v>
       </c>
     </row>
+    <row r="910" spans="1:5">
+      <c r="A910" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B910">
+        <v>12239.83</v>
+      </c>
+      <c r="C910">
+        <v>182.3</v>
+      </c>
+      <c r="D910">
+        <v>5046.84</v>
+      </c>
+      <c r="E910">
+        <v>3864.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E910"/>
+  <dimension ref="A1:E911"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15863,6 +15863,23 @@
         <v>3864.3</v>
       </c>
     </row>
+    <row r="911" spans="1:5">
+      <c r="A911" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B911">
+        <v>12086.89</v>
+      </c>
+      <c r="C911">
+        <v>181.11</v>
+      </c>
+      <c r="D911">
+        <v>5079.32</v>
+      </c>
+      <c r="E911">
+        <v>3786.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E911"/>
+  <dimension ref="A1:E912"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15880,6 +15880,23 @@
         <v>3786.3</v>
       </c>
     </row>
+    <row r="912" spans="1:5">
+      <c r="A912" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B912">
+        <v>11972.94</v>
+      </c>
+      <c r="C912">
+        <v>179.68</v>
+      </c>
+      <c r="D912">
+        <v>5130.31</v>
+      </c>
+      <c r="E912">
+        <v>3689.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/cbr/data/cb_metalls.xlsx
+++ b/LME/parser/cbr/data/cb_metalls.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E912"/>
+  <dimension ref="A1:E913"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -15897,6 +15897,23 @@
         <v>3689.59</v>
       </c>
     </row>
+    <row r="913" spans="1:5">
+      <c r="A913" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B913">
+        <v>11825.66</v>
+      </c>
+      <c r="C913">
+        <v>178</v>
+      </c>
+      <c r="D913">
+        <v>4905.31</v>
+      </c>
+      <c r="E913">
+        <v>3523.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
